--- a/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
+++ b/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\gcondorenz\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\1. Página Web\2026 - 06. Junio\Cemento 04-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28955BA-0A40-40AD-B47E-88BE13EEA05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="28680" yWindow="270" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C2" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="28">
   <si>
     <t>PERIODO</t>
   </si>
@@ -123,44 +124,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(p)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : Preliminar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(1):</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Comprende los volúmenes de cemento comercializados que reportan las empresas productoras.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>2026</t>
     </r>
     <r>
@@ -198,11 +161,17 @@
       <t xml:space="preserve"> DE CEMENTO POR DEPARTAMENTO SEGÚN AÑO Y MES, 1991 - 2026</t>
     </r>
   </si>
+  <si>
+    <t>(p): Preliminar</t>
+  </si>
+  <si>
+    <t>(1): Comprende los volúmenes de cemento comercializados que reportan las empresas productoras.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
@@ -274,12 +243,6 @@
       <family val="2"/>
     </font>
     <font>
-      <vertAlign val="superscript"/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <vertAlign val="superscript"/>
       <sz val="10"/>
@@ -312,6 +275,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -449,7 +417,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -466,22 +434,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -515,9 +483,6 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -533,9 +498,12 @@
     <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -675,6 +643,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -710,6 +695,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -885,7 +887,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG505"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1406,7 +1408,7 @@
     <row r="1" spans="2:16" ht="75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -15206,7 +15208,7 @@
       <c r="G468" s="21">
         <v>258524.41999999998</v>
       </c>
-      <c r="H468" s="29">
+      <c r="H468" s="28">
         <v>1053147.0159500015</v>
       </c>
       <c r="I468" s="21">
@@ -15239,7 +15241,7 @@
       <c r="G469" s="20">
         <v>19494.300000000003</v>
       </c>
-      <c r="H469" s="30">
+      <c r="H469" s="29">
         <v>99071.219999999797</v>
       </c>
       <c r="I469" s="20">
@@ -15272,7 +15274,7 @@
       <c r="G470" s="20">
         <v>26581.329999999998</v>
       </c>
-      <c r="H470" s="30">
+      <c r="H470" s="29">
         <v>69738.929999999556</v>
       </c>
       <c r="I470" s="20">
@@ -15305,7 +15307,7 @@
       <c r="G471" s="20">
         <v>13727.439999999999</v>
       </c>
-      <c r="H471" s="31">
+      <c r="H471" s="30">
         <v>78610.679999999455</v>
       </c>
       <c r="I471" s="20">
@@ -15338,7 +15340,7 @@
       <c r="G472" s="20">
         <v>19730.099999999999</v>
       </c>
-      <c r="H472" s="31">
+      <c r="H472" s="30">
         <v>82941.330000000249</v>
       </c>
       <c r="I472" s="20">
@@ -15371,7 +15373,7 @@
       <c r="G473" s="20">
         <v>17259.61</v>
       </c>
-      <c r="H473" s="31">
+      <c r="H473" s="30">
         <v>85540.270000000062</v>
       </c>
       <c r="I473" s="20">
@@ -15404,7 +15406,7 @@
       <c r="G474" s="20">
         <v>17687.330000000002</v>
       </c>
-      <c r="H474" s="31">
+      <c r="H474" s="30">
         <v>90002.610000000059</v>
       </c>
       <c r="I474" s="20">
@@ -15437,7 +15439,7 @@
       <c r="G475" s="20">
         <v>20019.14</v>
       </c>
-      <c r="H475" s="31">
+      <c r="H475" s="30">
         <v>91256.230000000069</v>
       </c>
       <c r="I475" s="20">
@@ -15470,7 +15472,7 @@
       <c r="G476" s="20">
         <v>23344.039999999997</v>
       </c>
-      <c r="H476" s="31">
+      <c r="H476" s="30">
         <v>96770.105950000754</v>
       </c>
       <c r="I476" s="20">
@@ -15503,7 +15505,7 @@
       <c r="G477" s="20">
         <v>21790.519999999997</v>
       </c>
-      <c r="H477" s="31">
+      <c r="H477" s="30">
         <v>99050.740000000762</v>
       </c>
       <c r="I477" s="20">
@@ -15536,7 +15538,7 @@
       <c r="G478" s="20">
         <v>28025.85</v>
       </c>
-      <c r="H478" s="31">
+      <c r="H478" s="30">
         <v>88553.55</v>
       </c>
       <c r="I478" s="20">
@@ -15569,7 +15571,7 @@
       <c r="G479" s="20">
         <v>22319.78</v>
       </c>
-      <c r="H479" s="31">
+      <c r="H479" s="30">
         <v>84343.09000000036</v>
       </c>
       <c r="I479" s="20">
@@ -15602,7 +15604,7 @@
       <c r="G480" s="20">
         <v>28544.979999999996</v>
       </c>
-      <c r="H480" s="31">
+      <c r="H480" s="30">
         <v>87268.260000000359</v>
       </c>
       <c r="I480" s="20">
@@ -15623,7 +15625,7 @@
       <c r="E481" s="20"/>
       <c r="F481" s="20"/>
       <c r="G481" s="20"/>
-      <c r="H481" s="31"/>
+      <c r="H481" s="30"/>
       <c r="I481" s="20"/>
       <c r="J481" s="23"/>
       <c r="K481" s="3"/>
@@ -15652,7 +15654,7 @@
       <c r="G482" s="21">
         <v>276840.12999999971</v>
       </c>
-      <c r="H482" s="29">
+      <c r="H482" s="28">
         <v>1062179.2699999984</v>
       </c>
       <c r="I482" s="21">
@@ -15685,7 +15687,7 @@
       <c r="G483" s="20">
         <v>15637.94</v>
       </c>
-      <c r="H483" s="30">
+      <c r="H483" s="29">
         <v>83691.060000000274</v>
       </c>
       <c r="I483" s="20">
@@ -15718,7 +15720,7 @@
       <c r="G484" s="20">
         <v>22037.41</v>
       </c>
-      <c r="H484" s="30">
+      <c r="H484" s="29">
         <v>93644.549999999028</v>
       </c>
       <c r="I484" s="20">
@@ -15751,7 +15753,7 @@
       <c r="G485" s="20">
         <v>14484.98</v>
       </c>
-      <c r="H485" s="30">
+      <c r="H485" s="29">
         <v>64027.439999999471</v>
       </c>
       <c r="I485" s="20">
@@ -15784,7 +15786,7 @@
       <c r="G486" s="20">
         <v>16302.65</v>
       </c>
-      <c r="H486" s="30">
+      <c r="H486" s="29">
         <v>81492.919999999547</v>
       </c>
       <c r="I486" s="20">
@@ -15817,7 +15819,7 @@
       <c r="G487" s="20">
         <v>31716.109999999986</v>
       </c>
-      <c r="H487" s="30">
+      <c r="H487" s="29">
         <v>90495.110000000146</v>
       </c>
       <c r="I487" s="20">
@@ -15850,7 +15852,7 @@
       <c r="G488" s="20">
         <v>29530.03</v>
       </c>
-      <c r="H488" s="30">
+      <c r="H488" s="29">
         <v>92038.98000000001</v>
       </c>
       <c r="I488" s="20">
@@ -15883,7 +15885,7 @@
       <c r="G489" s="20">
         <v>27151.97</v>
       </c>
-      <c r="H489" s="30">
+      <c r="H489" s="29">
         <v>117120.80000000002</v>
       </c>
       <c r="I489" s="20">
@@ -15916,7 +15918,7 @@
       <c r="G490" s="20">
         <v>19661.05</v>
       </c>
-      <c r="H490" s="30">
+      <c r="H490" s="29">
         <v>98461.479999999967</v>
       </c>
       <c r="I490" s="20">
@@ -15949,7 +15951,7 @@
       <c r="G491" s="20">
         <v>25715.569999999898</v>
       </c>
-      <c r="H491" s="30">
+      <c r="H491" s="29">
         <v>87374.97</v>
       </c>
       <c r="I491" s="20">
@@ -15982,7 +15984,7 @@
       <c r="G492" s="20">
         <v>32501.97</v>
       </c>
-      <c r="H492" s="30">
+      <c r="H492" s="29">
         <v>75107.5799999999</v>
       </c>
       <c r="I492" s="20">
@@ -16015,7 +16017,7 @@
       <c r="G493" s="20">
         <v>20729.289999999899</v>
       </c>
-      <c r="H493" s="30">
+      <c r="H493" s="29">
         <v>91275.959999999992</v>
       </c>
       <c r="I493" s="20">
@@ -16048,7 +16050,7 @@
       <c r="G494" s="20">
         <v>21371.16</v>
       </c>
-      <c r="H494" s="30">
+      <c r="H494" s="29">
         <v>87448.419999999911</v>
       </c>
       <c r="I494" s="20">
@@ -16069,7 +16071,7 @@
       <c r="E495" s="20"/>
       <c r="F495" s="20"/>
       <c r="G495" s="20"/>
-      <c r="H495" s="30"/>
+      <c r="H495" s="29"/>
       <c r="I495" s="20"/>
       <c r="J495" s="23"/>
       <c r="K495" s="3"/>
@@ -16081,28 +16083,28 @@
     </row>
     <row r="496" spans="2:16" ht="13.5" x14ac:dyDescent="0.2">
       <c r="B496" s="15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C496" s="21">
-        <v>170005.19</v>
+        <v>226598.64</v>
       </c>
       <c r="D496" s="21">
-        <v>94037.997999999905</v>
+        <v>141360.29799999989</v>
       </c>
       <c r="E496" s="21">
-        <v>60261.97</v>
+        <v>94976.430000000008</v>
       </c>
       <c r="F496" s="21">
-        <v>95123.469999999899</v>
+        <v>124827.86999999991</v>
       </c>
       <c r="G496" s="21">
-        <v>51480.480000000003</v>
-      </c>
-      <c r="H496" s="29">
-        <v>241660.52999999997</v>
+        <v>64308.87999999999</v>
+      </c>
+      <c r="H496" s="21">
+        <v>318871.52999999985</v>
       </c>
       <c r="I496" s="21">
-        <v>712569.6379999998</v>
+        <v>970943.6479999997</v>
       </c>
       <c r="J496" s="23"/>
       <c r="K496" s="3"/>
@@ -16131,7 +16133,7 @@
       <c r="G497" s="20">
         <v>16082.5</v>
       </c>
-      <c r="H497" s="30">
+      <c r="H497" s="29">
         <v>96316.08</v>
       </c>
       <c r="I497" s="20">
@@ -16164,7 +16166,7 @@
       <c r="G498" s="20">
         <v>16592.66</v>
       </c>
-      <c r="H498" s="30">
+      <c r="H498" s="29">
         <v>65909.01999999999</v>
       </c>
       <c r="I498" s="20">
@@ -16197,7 +16199,7 @@
       <c r="G499" s="20">
         <v>18805.320000000003</v>
       </c>
-      <c r="H499" s="30">
+      <c r="H499" s="29">
         <v>79435.429999999993</v>
       </c>
       <c r="I499" s="20">
@@ -16212,14 +16214,30 @@
       <c r="P499" s="3"/>
     </row>
     <row r="500" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B500" s="19"/>
-      <c r="C500" s="22"/>
-      <c r="D500" s="22"/>
-      <c r="E500" s="22"/>
-      <c r="F500" s="22"/>
-      <c r="G500" s="22"/>
-      <c r="H500" s="34"/>
-      <c r="I500" s="22"/>
+      <c r="B500" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C500" s="22">
+        <v>56593.45</v>
+      </c>
+      <c r="D500" s="22">
+        <v>47322.3</v>
+      </c>
+      <c r="E500" s="22">
+        <v>34714.460000000006</v>
+      </c>
+      <c r="F500" s="22">
+        <v>29704.400000000001</v>
+      </c>
+      <c r="G500" s="22">
+        <v>12828.399999999991</v>
+      </c>
+      <c r="H500" s="32">
+        <v>77210.999999999898</v>
+      </c>
+      <c r="I500" s="22">
+        <v>258374.00999999989</v>
+      </c>
       <c r="J500" s="23"/>
       <c r="K500" s="3"/>
       <c r="L500" s="3"/>
@@ -16232,13 +16250,13 @@
       <c r="B501" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="C501" s="32"/>
-      <c r="D501" s="32"/>
-      <c r="E501" s="32"/>
-      <c r="F501" s="32"/>
-      <c r="G501" s="32"/>
-      <c r="H501" s="32"/>
-      <c r="I501" s="32"/>
+      <c r="C501" s="31"/>
+      <c r="D501" s="31"/>
+      <c r="E501" s="31"/>
+      <c r="F501" s="31"/>
+      <c r="G501" s="31"/>
+      <c r="H501" s="31"/>
+      <c r="I501" s="31"/>
       <c r="J501" s="23"/>
       <c r="K501" s="3"/>
       <c r="L501" s="3"/>
@@ -16248,14 +16266,14 @@
       <c r="P501" s="3"/>
     </row>
     <row r="502" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B502" s="27" t="s">
-        <v>24</v>
+      <c r="B502" s="34" t="s">
+        <v>26</v>
       </c>
       <c r="H502" s="4"/>
     </row>
     <row r="503" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B503" s="27" t="s">
-        <v>25</v>
+      <c r="B503" s="34" t="s">
+        <v>27</v>
       </c>
       <c r="H503" s="4"/>
     </row>
@@ -16263,13 +16281,13 @@
       <c r="H504" s="4"/>
     </row>
     <row r="505" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C505" s="28"/>
-      <c r="D505" s="28"/>
-      <c r="E505" s="28"/>
-      <c r="F505" s="28"/>
-      <c r="G505" s="28"/>
-      <c r="H505" s="28"/>
-      <c r="I505" s="28"/>
+      <c r="C505" s="27"/>
+      <c r="D505" s="27"/>
+      <c r="E505" s="27"/>
+      <c r="F505" s="27"/>
+      <c r="G505" s="27"/>
+      <c r="H505" s="27"/>
+      <c r="I505" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
+++ b/datos/indicadores_adelantados/cemento/ventas_cemento_depto_1991_2026.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\1. Página Web\2026 - 06. Junio\Cemento 04-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\3. IGAE\2026-08 Agosto\5. Cemento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28955BA-0A40-40AD-B47E-88BE13EEA05B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="270" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10605" windowHeight="11010"/>
   </bookViews>
   <sheets>
     <sheet name="C2" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="26">
   <si>
     <t>PERIODO</t>
   </si>
@@ -90,12 +89,11 @@
     <t>(En toneladas métricas)</t>
   </si>
   <si>
-    <r>
-      <t>2024</t>
-    </r>
+    <t xml:space="preserve">Fuente: Empresas productoras de cemento </t>
+  </si>
+  <si>
     <r>
       <rPr>
-        <b/>
         <vertAlign val="superscript"/>
         <sz val="9"/>
         <rFont val="Arial"/>
@@ -103,24 +101,33 @@
       </rPr>
       <t>(p)</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> : Preliminar</t>
+    </r>
   </si>
   <si>
     <r>
-      <t>2025</t>
-    </r>
-    <r>
       <rPr>
-        <b/>
         <vertAlign val="superscript"/>
         <sz val="9"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>(p)</t>
+      <t>(1):</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente: Empresas productoras de cemento </t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Comprende los volúmenes de cemento comercializados que reportan las empresas productoras.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -161,17 +168,11 @@
       <t xml:space="preserve"> DE CEMENTO POR DEPARTAMENTO SEGÚN AÑO Y MES, 1991 - 2026</t>
     </r>
   </si>
-  <si>
-    <t>(p): Preliminar</t>
-  </si>
-  <si>
-    <t>(1): Comprende los volúmenes de cemento comercializados que reportan las empresas productoras.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
@@ -243,6 +244,12 @@
       <family val="2"/>
     </font>
     <font>
+      <vertAlign val="superscript"/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <vertAlign val="superscript"/>
       <sz val="10"/>
@@ -275,11 +282,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -417,7 +419,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -434,22 +436,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -483,6 +485,9 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -498,12 +503,9 @@
     <xf numFmtId="3" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -643,23 +645,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -695,23 +680,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -887,8 +855,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG505"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AG508"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
@@ -15190,8 +15158,8 @@
       <c r="P467" s="3"/>
     </row>
     <row r="468" spans="2:16" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="B468" s="15" t="s">
-        <v>21</v>
+      <c r="B468" s="15">
+        <v>2024</v>
       </c>
       <c r="C468" s="21">
         <v>788377.11</v>
@@ -15208,7 +15176,7 @@
       <c r="G468" s="21">
         <v>258524.41999999998</v>
       </c>
-      <c r="H468" s="28">
+      <c r="H468" s="29">
         <v>1053147.0159500015</v>
       </c>
       <c r="I468" s="21">
@@ -15241,7 +15209,7 @@
       <c r="G469" s="20">
         <v>19494.300000000003</v>
       </c>
-      <c r="H469" s="29">
+      <c r="H469" s="30">
         <v>99071.219999999797</v>
       </c>
       <c r="I469" s="20">
@@ -15274,7 +15242,7 @@
       <c r="G470" s="20">
         <v>26581.329999999998</v>
       </c>
-      <c r="H470" s="29">
+      <c r="H470" s="30">
         <v>69738.929999999556</v>
       </c>
       <c r="I470" s="20">
@@ -15307,7 +15275,7 @@
       <c r="G471" s="20">
         <v>13727.439999999999</v>
       </c>
-      <c r="H471" s="30">
+      <c r="H471" s="31">
         <v>78610.679999999455</v>
       </c>
       <c r="I471" s="20">
@@ -15340,7 +15308,7 @@
       <c r="G472" s="20">
         <v>19730.099999999999</v>
       </c>
-      <c r="H472" s="30">
+      <c r="H472" s="31">
         <v>82941.330000000249</v>
       </c>
       <c r="I472" s="20">
@@ -15373,7 +15341,7 @@
       <c r="G473" s="20">
         <v>17259.61</v>
       </c>
-      <c r="H473" s="30">
+      <c r="H473" s="31">
         <v>85540.270000000062</v>
       </c>
       <c r="I473" s="20">
@@ -15406,7 +15374,7 @@
       <c r="G474" s="20">
         <v>17687.330000000002</v>
       </c>
-      <c r="H474" s="30">
+      <c r="H474" s="31">
         <v>90002.610000000059</v>
       </c>
       <c r="I474" s="20">
@@ -15439,7 +15407,7 @@
       <c r="G475" s="20">
         <v>20019.14</v>
       </c>
-      <c r="H475" s="30">
+      <c r="H475" s="31">
         <v>91256.230000000069</v>
       </c>
       <c r="I475" s="20">
@@ -15472,7 +15440,7 @@
       <c r="G476" s="20">
         <v>23344.039999999997</v>
       </c>
-      <c r="H476" s="30">
+      <c r="H476" s="31">
         <v>96770.105950000754</v>
       </c>
       <c r="I476" s="20">
@@ -15505,7 +15473,7 @@
       <c r="G477" s="20">
         <v>21790.519999999997</v>
       </c>
-      <c r="H477" s="30">
+      <c r="H477" s="31">
         <v>99050.740000000762</v>
       </c>
       <c r="I477" s="20">
@@ -15538,7 +15506,7 @@
       <c r="G478" s="20">
         <v>28025.85</v>
       </c>
-      <c r="H478" s="30">
+      <c r="H478" s="31">
         <v>88553.55</v>
       </c>
       <c r="I478" s="20">
@@ -15571,7 +15539,7 @@
       <c r="G479" s="20">
         <v>22319.78</v>
       </c>
-      <c r="H479" s="30">
+      <c r="H479" s="31">
         <v>84343.09000000036</v>
       </c>
       <c r="I479" s="20">
@@ -15604,7 +15572,7 @@
       <c r="G480" s="20">
         <v>28544.979999999996</v>
       </c>
-      <c r="H480" s="30">
+      <c r="H480" s="31">
         <v>87268.260000000359</v>
       </c>
       <c r="I480" s="20">
@@ -15625,7 +15593,7 @@
       <c r="E481" s="20"/>
       <c r="F481" s="20"/>
       <c r="G481" s="20"/>
-      <c r="H481" s="30"/>
+      <c r="H481" s="31"/>
       <c r="I481" s="20"/>
       <c r="J481" s="23"/>
       <c r="K481" s="3"/>
@@ -15636,8 +15604,8 @@
       <c r="P481" s="3"/>
     </row>
     <row r="482" spans="2:16" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="B482" s="15" t="s">
-        <v>22</v>
+      <c r="B482" s="15">
+        <v>2025</v>
       </c>
       <c r="C482" s="21">
         <v>745053.49</v>
@@ -15654,7 +15622,7 @@
       <c r="G482" s="21">
         <v>276840.12999999971</v>
       </c>
-      <c r="H482" s="28">
+      <c r="H482" s="29">
         <v>1062179.2699999984</v>
       </c>
       <c r="I482" s="21">
@@ -15687,7 +15655,7 @@
       <c r="G483" s="20">
         <v>15637.94</v>
       </c>
-      <c r="H483" s="29">
+      <c r="H483" s="30">
         <v>83691.060000000274</v>
       </c>
       <c r="I483" s="20">
@@ -15720,7 +15688,7 @@
       <c r="G484" s="20">
         <v>22037.41</v>
       </c>
-      <c r="H484" s="29">
+      <c r="H484" s="30">
         <v>93644.549999999028</v>
       </c>
       <c r="I484" s="20">
@@ -15753,7 +15721,7 @@
       <c r="G485" s="20">
         <v>14484.98</v>
       </c>
-      <c r="H485" s="29">
+      <c r="H485" s="30">
         <v>64027.439999999471</v>
       </c>
       <c r="I485" s="20">
@@ -15786,7 +15754,7 @@
       <c r="G486" s="20">
         <v>16302.65</v>
       </c>
-      <c r="H486" s="29">
+      <c r="H486" s="30">
         <v>81492.919999999547</v>
       </c>
       <c r="I486" s="20">
@@ -15819,7 +15787,7 @@
       <c r="G487" s="20">
         <v>31716.109999999986</v>
       </c>
-      <c r="H487" s="29">
+      <c r="H487" s="30">
         <v>90495.110000000146</v>
       </c>
       <c r="I487" s="20">
@@ -15852,7 +15820,7 @@
       <c r="G488" s="20">
         <v>29530.03</v>
       </c>
-      <c r="H488" s="29">
+      <c r="H488" s="30">
         <v>92038.98000000001</v>
       </c>
       <c r="I488" s="20">
@@ -15885,7 +15853,7 @@
       <c r="G489" s="20">
         <v>27151.97</v>
       </c>
-      <c r="H489" s="29">
+      <c r="H489" s="30">
         <v>117120.80000000002</v>
       </c>
       <c r="I489" s="20">
@@ -15918,7 +15886,7 @@
       <c r="G490" s="20">
         <v>19661.05</v>
       </c>
-      <c r="H490" s="29">
+      <c r="H490" s="30">
         <v>98461.479999999967</v>
       </c>
       <c r="I490" s="20">
@@ -15951,7 +15919,7 @@
       <c r="G491" s="20">
         <v>25715.569999999898</v>
       </c>
-      <c r="H491" s="29">
+      <c r="H491" s="30">
         <v>87374.97</v>
       </c>
       <c r="I491" s="20">
@@ -15984,7 +15952,7 @@
       <c r="G492" s="20">
         <v>32501.97</v>
       </c>
-      <c r="H492" s="29">
+      <c r="H492" s="30">
         <v>75107.5799999999</v>
       </c>
       <c r="I492" s="20">
@@ -16017,7 +15985,7 @@
       <c r="G493" s="20">
         <v>20729.289999999899</v>
       </c>
-      <c r="H493" s="29">
+      <c r="H493" s="30">
         <v>91275.959999999992</v>
       </c>
       <c r="I493" s="20">
@@ -16050,7 +16018,7 @@
       <c r="G494" s="20">
         <v>21371.16</v>
       </c>
-      <c r="H494" s="29">
+      <c r="H494" s="30">
         <v>87448.419999999911</v>
       </c>
       <c r="I494" s="20">
@@ -16071,7 +16039,7 @@
       <c r="E495" s="20"/>
       <c r="F495" s="20"/>
       <c r="G495" s="20"/>
-      <c r="H495" s="29"/>
+      <c r="H495" s="30"/>
       <c r="I495" s="20"/>
       <c r="J495" s="23"/>
       <c r="K495" s="3"/>
@@ -16086,25 +16054,25 @@
         <v>24</v>
       </c>
       <c r="C496" s="21">
-        <v>226598.64</v>
+        <v>314822.24</v>
       </c>
       <c r="D496" s="21">
-        <v>141360.29799999989</v>
+        <v>193122.90799999988</v>
       </c>
       <c r="E496" s="21">
-        <v>94976.430000000008</v>
+        <v>186518.26</v>
       </c>
       <c r="F496" s="21">
-        <v>124827.86999999991</v>
+        <v>163371.61999999991</v>
       </c>
       <c r="G496" s="21">
-        <v>64308.87999999999</v>
+        <v>92915.019999999873</v>
       </c>
       <c r="H496" s="21">
-        <v>318871.52999999985</v>
+        <v>454048.03899999987</v>
       </c>
       <c r="I496" s="21">
-        <v>970943.6479999997</v>
+        <v>1404798.0869999996</v>
       </c>
       <c r="J496" s="23"/>
       <c r="K496" s="3"/>
@@ -16133,7 +16101,7 @@
       <c r="G497" s="20">
         <v>16082.5</v>
       </c>
-      <c r="H497" s="29">
+      <c r="H497" s="30">
         <v>96316.08</v>
       </c>
       <c r="I497" s="20">
@@ -16166,7 +16134,7 @@
       <c r="G498" s="20">
         <v>16592.66</v>
       </c>
-      <c r="H498" s="29">
+      <c r="H498" s="30">
         <v>65909.01999999999</v>
       </c>
       <c r="I498" s="20">
@@ -16199,7 +16167,7 @@
       <c r="G499" s="20">
         <v>18805.320000000003</v>
       </c>
-      <c r="H499" s="29">
+      <c r="H499" s="30">
         <v>79435.429999999993</v>
       </c>
       <c r="I499" s="20">
@@ -16214,28 +16182,28 @@
       <c r="P499" s="3"/>
     </row>
     <row r="500" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B500" s="19" t="s">
+      <c r="B500" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C500" s="22">
+      <c r="C500" s="20">
         <v>56593.45</v>
       </c>
-      <c r="D500" s="22">
+      <c r="D500" s="20">
         <v>47322.3</v>
       </c>
-      <c r="E500" s="22">
+      <c r="E500" s="20">
         <v>34714.460000000006</v>
       </c>
-      <c r="F500" s="22">
+      <c r="F500" s="20">
         <v>29704.400000000001</v>
       </c>
-      <c r="G500" s="22">
+      <c r="G500" s="20">
         <v>12828.399999999991</v>
       </c>
-      <c r="H500" s="32">
+      <c r="H500" s="30">
         <v>77210.999999999898</v>
       </c>
-      <c r="I500" s="22">
+      <c r="I500" s="20">
         <v>258374.00999999989</v>
       </c>
       <c r="J500" s="23"/>
@@ -16247,16 +16215,30 @@
       <c r="P500" s="3"/>
     </row>
     <row r="501" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="B501" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="C501" s="31"/>
-      <c r="D501" s="31"/>
-      <c r="E501" s="31"/>
-      <c r="F501" s="31"/>
-      <c r="G501" s="31"/>
-      <c r="H501" s="31"/>
-      <c r="I501" s="31"/>
+      <c r="B501" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C501" s="20">
+        <v>48111.000000000007</v>
+      </c>
+      <c r="D501" s="20">
+        <v>4169.49</v>
+      </c>
+      <c r="E501" s="20">
+        <v>35745.96</v>
+      </c>
+      <c r="F501" s="20">
+        <v>35473.25</v>
+      </c>
+      <c r="G501" s="20">
+        <v>12454.55999999999</v>
+      </c>
+      <c r="H501" s="30">
+        <v>74749.570000000007</v>
+      </c>
+      <c r="I501" s="20">
+        <v>210703.83000000002</v>
+      </c>
       <c r="J501" s="23"/>
       <c r="K501" s="3"/>
       <c r="L501" s="3"/>
@@ -16265,29 +16247,98 @@
       <c r="O501" s="3"/>
       <c r="P501" s="3"/>
     </row>
-    <row r="502" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B502" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="H502" s="4"/>
-    </row>
-    <row r="503" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B503" s="34" t="s">
-        <v>27</v>
-      </c>
-      <c r="H503" s="4"/>
-    </row>
-    <row r="504" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="H504" s="4"/>
+    <row r="502" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B502" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C502" s="20">
+        <v>40112.6</v>
+      </c>
+      <c r="D502" s="20">
+        <v>47593.119999999981</v>
+      </c>
+      <c r="E502" s="20">
+        <v>55795.87</v>
+      </c>
+      <c r="F502" s="20">
+        <v>3070.5</v>
+      </c>
+      <c r="G502" s="20">
+        <v>16151.5799999999</v>
+      </c>
+      <c r="H502" s="30">
+        <v>60426.938999999998</v>
+      </c>
+      <c r="I502" s="20">
+        <v>223150.60899999988</v>
+      </c>
+      <c r="J502" s="23"/>
+      <c r="K502" s="3"/>
+      <c r="L502" s="3"/>
+      <c r="M502" s="3"/>
+      <c r="N502" s="3"/>
+      <c r="O502" s="3"/>
+      <c r="P502" s="3"/>
+    </row>
+    <row r="503" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B503" s="19"/>
+      <c r="C503" s="22"/>
+      <c r="D503" s="22"/>
+      <c r="E503" s="22"/>
+      <c r="F503" s="22"/>
+      <c r="G503" s="22"/>
+      <c r="H503" s="34"/>
+      <c r="I503" s="22"/>
+      <c r="J503" s="23"/>
+      <c r="K503" s="3"/>
+      <c r="L503" s="3"/>
+      <c r="M503" s="3"/>
+      <c r="N503" s="3"/>
+      <c r="O503" s="3"/>
+      <c r="P503" s="3"/>
+    </row>
+    <row r="504" spans="2:16" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="B504" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="C504" s="32"/>
+      <c r="D504" s="32"/>
+      <c r="E504" s="32"/>
+      <c r="F504" s="32"/>
+      <c r="G504" s="32"/>
+      <c r="H504" s="32"/>
+      <c r="I504" s="32"/>
+      <c r="J504" s="23"/>
+      <c r="K504" s="3"/>
+      <c r="L504" s="3"/>
+      <c r="M504" s="3"/>
+      <c r="N504" s="3"/>
+      <c r="O504" s="3"/>
+      <c r="P504" s="3"/>
     </row>
     <row r="505" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="C505" s="27"/>
-      <c r="D505" s="27"/>
-      <c r="E505" s="27"/>
-      <c r="F505" s="27"/>
-      <c r="G505" s="27"/>
-      <c r="H505" s="27"/>
-      <c r="I505" s="27"/>
+      <c r="B505" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="H505" s="4"/>
+    </row>
+    <row r="506" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B506" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="H506" s="4"/>
+    </row>
+    <row r="507" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="H507" s="4"/>
+    </row>
+    <row r="508" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C508" s="28"/>
+      <c r="D508" s="28"/>
+      <c r="E508" s="28"/>
+      <c r="F508" s="28"/>
+      <c r="G508" s="28"/>
+      <c r="H508" s="28"/>
+      <c r="I508" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
